--- a/public/plantillas/plantilla_importar_productos.xlsx
+++ b/public/plantillas/plantilla_importar_productos.xlsx
@@ -1,62 +1,171 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr/>
-  <workbookProtection/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ANTHONY\Downloads\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7050"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Productos" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instrucciones" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Productos" sheetId="1" r:id="rId1"/>
+    <sheet name="Instrucciones" sheetId="2" r:id="rId2"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="33">
+  <si>
+    <t>Producto</t>
+  </si>
+  <si>
+    <t>Categoria</t>
+  </si>
+  <si>
+    <t>Color</t>
+  </si>
+  <si>
+    <t>Talla</t>
+  </si>
+  <si>
+    <t>Precio Compra</t>
+  </si>
+  <si>
+    <t>Precio Venta</t>
+  </si>
+  <si>
+    <t>Stock</t>
+  </si>
+  <si>
+    <t>Polo Bebe Tee</t>
+  </si>
+  <si>
+    <t>Superior</t>
+  </si>
+  <si>
+    <t>Azul</t>
+  </si>
+  <si>
+    <t>M</t>
+  </si>
+  <si>
+    <t>INSTRUCCIONES PARA LLENAR ESTA PLANTILLA</t>
+  </si>
+  <si>
+    <t>1. No cambies los nombres de las columnas de la hoja 'Productos'.</t>
+  </si>
+  <si>
+    <t>2. La fila 2 es un EJEMPLO (en gris/cursiva) - borrala y escribe tus propios productos debajo.</t>
+  </si>
+  <si>
+    <t>3. Producto: el nombre del producto (ej: Polo Bebe Tee, Pantalon Cataneas).</t>
+  </si>
+  <si>
+    <t>4. Categoria: el nombre de la categoria (si no existe, el sistema la crea automaticamente).</t>
+  </si>
+  <si>
+    <t>5. Color: el color de esa variante especifica.</t>
+  </si>
+  <si>
+    <t>6. Talla: debe ser una talla que ya este activada en tu sistema (ej: S, M, L, 38, 40).</t>
+  </si>
+  <si>
+    <t>7. Precio Compra / Precio Venta: usa solo numeros, sin el simbolo S/ (ej: 20, no S/20.00).</t>
+  </si>
+  <si>
+    <t>8. Stock: la cantidad inicial que tienes de esa variante.</t>
+  </si>
+  <si>
+    <t>9. Cada fila es UNA variante (una combinacion de producto+color+talla).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   Si el mismo producto tiene varios colores o tallas, repite el nombre del producto</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   en varias filas, una por cada variante.</t>
+  </si>
+  <si>
+    <t>10. Guarda el archivo y subelo en el sistema, en Productos &gt; Importar desde Excel.</t>
+  </si>
+  <si>
+    <t>patalon palazo cuba</t>
+  </si>
+  <si>
+    <t>S</t>
+  </si>
+  <si>
+    <t>L</t>
+  </si>
+  <si>
+    <t>Inferior</t>
+  </si>
+  <si>
+    <t>Falda Short</t>
+  </si>
+  <si>
+    <t>Negro</t>
+  </si>
+  <si>
+    <t>Blanco</t>
+  </si>
+  <si>
+    <t>Beige</t>
+  </si>
+  <si>
+    <t>Marron</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="5">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
     </font>
     <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF808080"/>
       <name val="Arial"/>
-      <i val="1"/>
-      <color rgb="00808080"/>
     </font>
     <font>
+      <b/>
+      <sz val="13"/>
       <name val="Arial"/>
-      <b val="1"/>
-      <sz val="13"/>
     </font>
     <font>
+      <sz val="11"/>
       <name val="Arial"/>
-      <sz val="11"/>
     </font>
   </fonts>
   <fills count="3">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="001F4E78"/>
-        <bgColor rgb="001F4E78"/>
+        <fgColor rgb="FF1F4E78"/>
+        <bgColor rgb="FF1F4E78"/>
       </patternFill>
     </fill>
   </fills>
@@ -73,86 +182,27 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="5">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -440,89 +490,292 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:G2"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:G12"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
+    <col min="1" max="1" width="22" customWidth="1"/>
+    <col min="2" max="2" width="16" customWidth="1"/>
+    <col min="3" max="3" width="14" customWidth="1"/>
+    <col min="4" max="4" width="10" customWidth="1"/>
+    <col min="5" max="6" width="14" customWidth="1"/>
+    <col min="7" max="7" width="10" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Producto</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Categoria</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Color</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Talla</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Precio Compra</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Precio Venta</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Stock</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Polo Bebe Tee</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>Superior</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>Azul</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="n">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2" s="2">
         <v>20</v>
       </c>
-      <c r="F2" s="2" t="n">
+      <c r="F2" s="2">
         <v>40</v>
       </c>
-      <c r="G2" s="2" t="n">
+      <c r="G2" s="2">
         <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D3" s="2">
+        <v>28</v>
+      </c>
+      <c r="E3" s="2">
+        <v>35</v>
+      </c>
+      <c r="F3" s="2">
+        <v>55</v>
+      </c>
+      <c r="G3" s="2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D4" s="2">
+        <v>30</v>
+      </c>
+      <c r="E4" s="2">
+        <v>35</v>
+      </c>
+      <c r="F4" s="2">
+        <v>55</v>
+      </c>
+      <c r="G4" s="2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D5" s="2">
+        <v>32</v>
+      </c>
+      <c r="E5" s="2">
+        <v>35</v>
+      </c>
+      <c r="F5" s="2">
+        <v>55</v>
+      </c>
+      <c r="G5" s="2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D6" s="2">
+        <v>34</v>
+      </c>
+      <c r="E6" s="2">
+        <v>35</v>
+      </c>
+      <c r="F6" s="2">
+        <v>55</v>
+      </c>
+      <c r="G6" s="2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A7" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E7" s="2">
+        <v>20</v>
+      </c>
+      <c r="F7" s="2">
+        <v>40</v>
+      </c>
+      <c r="G7" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A8" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E8" s="2">
+        <v>20</v>
+      </c>
+      <c r="F8" s="2">
+        <v>40</v>
+      </c>
+      <c r="G8" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A9" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="E9" s="2">
+        <v>20</v>
+      </c>
+      <c r="F9" s="2">
+        <v>40</v>
+      </c>
+      <c r="G9" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A10" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E10" s="2">
+        <v>20</v>
+      </c>
+      <c r="F10" s="2">
+        <v>40</v>
+      </c>
+      <c r="G10" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A11" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E11" s="2">
+        <v>20</v>
+      </c>
+      <c r="F11" s="2">
+        <v>40</v>
+      </c>
+      <c r="G11" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A12" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="E12" s="2">
+        <v>20</v>
+      </c>
+      <c r="F12" s="2">
+        <v>40</v>
+      </c>
+      <c r="G12" s="2">
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -531,109 +784,79 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:A14"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col width="100" customWidth="1" min="1" max="1"/>
+    <col min="1" max="1" width="100" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="3" t="inlineStr">
-        <is>
-          <t>INSTRUCCIONES PARA LLENAR ESTA PLANTILLA</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="4" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>1. No cambies los nombres de las columnas de la hoja 'Productos'.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="4" t="inlineStr">
-        <is>
-          <t>2. La fila 2 es un EJEMPLO (en gris/cursiva) - borrala y escribe tus propios productos debajo.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t>3. Producto: el nombre del producto (ej: Polo Bebe Tee, Pantalon Cataneas).</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>4. Categoria: el nombre de la categoria (si no existe, el sistema la crea automaticamente).</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="4" t="inlineStr">
-        <is>
-          <t>5. Color: el color de esa variante especifica.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="4" t="inlineStr">
-        <is>
-          <t>6. Talla: debe ser una talla que ya este activada en tu sistema (ej: S, M, L, 38, 40).</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="4" t="inlineStr">
-        <is>
-          <t>7. Precio Compra / Precio Venta: usa solo numeros, sin el simbolo S/ (ej: 20, no S/20.00).</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="4" t="inlineStr">
-        <is>
-          <t>8. Stock: la cantidad inicial que tienes de esa variante.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="4" t="inlineStr">
-        <is>
-          <t>9. Cada fila es UNA variante (una combinacion de producto+color+talla).</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   Si el mismo producto tiene varios colores o tallas, repite el nombre del producto</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   en varias filas, una por cada variante.</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="4" t="inlineStr">
-        <is>
-          <t>10. Guarda el archivo y subelo en el sistema, en Productos &gt; Importar desde Excel.</t>
-        </is>
+    <row r="1" spans="1:1" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A1" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2" s="4"/>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3" s="4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A4" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A5" s="4" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A6" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A7" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A8" s="4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A9" s="4" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A10" s="4" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A11" s="4" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A12" s="4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A13" s="4" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A14" s="4" t="s">
+        <v>23</v>
       </c>
     </row>
   </sheetData>
